--- a/specification_generator/PROYECTOIA/METODOS_LAB/TRADUCCIONES_ESPECIFICACIONES.xlsx
+++ b/specification_generator/PROYECTOIA/METODOS_LAB/TRADUCCIONES_ESPECIFICACIONES.xlsx
@@ -6657,7 +6657,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>ANEX</t>
+          <t>ANNEX</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>ANEX</t>
+          <t>ANNEX</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
